--- a/events/Prague_2016_WC/Prague_2016_WC_start.xlsx
+++ b/events/Prague_2016_WC/Prague_2016_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W602"/>
+  <dimension ref="A1:AC602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1625,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -1653,7 +1683,7 @@
           <t>MUSEVYCH Vadym</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35525</t>
         </is>
@@ -1711,7 +1741,7 @@
           <t>LOWTHER Steven</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>44811</t>
         </is>
@@ -1769,7 +1799,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -1827,7 +1857,7 @@
           <t>McEWAN Devin</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -1938,7 +1968,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -1996,7 +2026,7 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -2054,7 +2084,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -2112,7 +2142,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -2170,7 +2200,7 @@
           <t>SUSLOV Alexei</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
@@ -2228,7 +2258,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -2286,7 +2316,7 @@
           <t>TANIGUCHI Kazuya</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>39699</t>
         </is>
@@ -2344,7 +2374,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -2402,7 +2432,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -2460,7 +2490,7 @@
           <t>PLEWA Przemyslaw</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>35950</t>
         </is>
@@ -2518,7 +2548,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -2576,7 +2606,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -2634,7 +2664,7 @@
           <t>SOETER Dennis</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>39166</t>
         </is>
@@ -2692,7 +2722,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -2750,7 +2780,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -2808,7 +2838,7 @@
           <t>FOULON Kilian</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>35602</t>
         </is>
@@ -2866,7 +2896,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -2924,7 +2954,7 @@
           <t>CHOOAMPAI Rattanajet</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>51801</t>
         </is>
@@ -2982,7 +3012,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -3040,7 +3070,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -3098,7 +3128,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -3209,7 +3239,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -3267,7 +3297,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -3325,7 +3355,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -3383,7 +3413,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -3441,7 +3471,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -3499,7 +3529,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -3557,7 +3587,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -3615,7 +3645,7 @@
           <t>COF Blaz</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>36897</t>
         </is>
@@ -3673,7 +3703,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -3731,7 +3761,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -3789,7 +3819,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -3847,7 +3877,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -3905,7 +3935,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -3963,7 +3993,7 @@
           <t>BREUER Florian</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>39171</t>
         </is>
@@ -4021,7 +4051,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -4079,7 +4109,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -4137,7 +4167,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -4195,7 +4225,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -4253,7 +4283,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -4311,7 +4341,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -4369,7 +4399,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -4427,7 +4457,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -4485,7 +4515,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -4543,7 +4573,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -4601,7 +4631,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -4659,7 +4689,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -4717,7 +4747,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -4775,7 +4805,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -4833,7 +4863,7 @@
           <t>ZHANG Jinjie</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>72213</t>
         </is>
@@ -4891,7 +4921,7 @@
           <t>WALL Demelza</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>60107</t>
         </is>
@@ -4949,7 +4979,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -5007,7 +5037,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -5171,7 +5201,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -5229,7 +5259,7 @@
           <t>KUBBE Kira</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
@@ -5287,7 +5317,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -5345,7 +5375,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -5403,7 +5433,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -5620,7 +5650,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -5678,7 +5708,7 @@
           <t>NAVEAU Laurine</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>53246</t>
         </is>
@@ -5736,7 +5766,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -5847,7 +5877,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -5905,7 +5935,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -5963,7 +5993,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -6021,7 +6051,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -6079,7 +6109,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -6137,7 +6167,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -6195,7 +6225,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -6253,7 +6283,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -6311,7 +6341,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -6369,7 +6399,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -6427,7 +6457,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -6485,7 +6515,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -6543,7 +6573,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -6601,7 +6631,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -6818,7 +6848,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -6876,7 +6906,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -6934,7 +6964,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -6992,7 +7022,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -7050,7 +7080,7 @@
           <t>LAUNAY Damien</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>60047</t>
         </is>
@@ -7108,7 +7138,7 @@
           <t>SHABAKIN Mikhail</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>73958</t>
         </is>
@@ -7166,7 +7196,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -7224,7 +7254,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -7282,7 +7312,7 @@
           <t>MUSGRAVE Andrew</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>60102</t>
         </is>
@@ -7340,7 +7370,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -7398,7 +7428,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -7456,7 +7486,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -7514,7 +7544,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -7572,7 +7602,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -7630,7 +7660,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -7688,7 +7718,7 @@
           <t>PROZHERIN Artem</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35775</t>
         </is>
@@ -7746,7 +7776,7 @@
           <t>TRAVOSTINO Benjamin</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>68795</t>
         </is>
@@ -7804,7 +7834,7 @@
           <t>SANDERA Wiktor</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>53642</t>
         </is>
@@ -7862,7 +7892,7 @@
           <t>LEE EDWARDS Ciaran</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>35614</t>
         </is>
@@ -7920,7 +7950,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -7978,7 +8008,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -8036,7 +8066,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -8094,7 +8124,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -8205,7 +8235,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -8263,7 +8293,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -8321,7 +8351,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -8379,7 +8409,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -8437,7 +8467,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -8495,7 +8525,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -8553,7 +8583,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -8611,7 +8641,7 @@
           <t>CADENA Jordi</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>41644</t>
         </is>
@@ -8669,7 +8699,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -8727,7 +8757,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -8785,7 +8815,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -8843,7 +8873,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -8901,7 +8931,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -8959,7 +8989,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -9017,7 +9047,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -9075,7 +9105,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -9133,7 +9163,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -9191,7 +9221,7 @@
           <t>HUJSA Matus</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35503</t>
         </is>
@@ -9249,7 +9279,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -9307,7 +9337,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -9365,7 +9395,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -9476,7 +9506,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -9534,7 +9564,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -9592,7 +9622,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -9650,7 +9680,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -9708,7 +9738,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -9766,7 +9796,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -9824,7 +9854,7 @@
           <t>DAILLE Etienne</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>35308</t>
         </is>
@@ -9882,7 +9912,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -9940,7 +9970,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -9998,7 +10028,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -10056,7 +10086,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -10114,7 +10144,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -10172,7 +10202,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -10230,7 +10260,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -10288,7 +10318,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -10346,7 +10376,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -10404,7 +10434,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -10462,7 +10492,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -10520,7 +10550,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -10578,7 +10608,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -10636,7 +10666,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -10694,7 +10724,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -10752,7 +10782,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -10810,7 +10840,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -10868,7 +10898,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -10926,7 +10956,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -10984,7 +11014,7 @@
           <t>MUSEVYCH Vadym</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>35525</t>
         </is>
@@ -11042,7 +11072,7 @@
           <t>LOWTHER Steven</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>44811</t>
         </is>
@@ -11100,7 +11130,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -11158,7 +11188,7 @@
           <t>McEWAN Devin</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -11269,7 +11299,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -11327,7 +11357,7 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -11385,7 +11415,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -11443,7 +11473,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -11501,7 +11531,7 @@
           <t>SUSLOV Alexei</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
@@ -11559,7 +11589,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -11617,7 +11647,7 @@
           <t>TANIGUCHI Kazuya</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>39699</t>
         </is>
@@ -11675,7 +11705,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -11733,7 +11763,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -11791,7 +11821,7 @@
           <t>PLEWA Przemyslaw</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>35950</t>
         </is>
@@ -11849,7 +11879,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -11907,7 +11937,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -11965,7 +11995,7 @@
           <t>SOETER Dennis</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>39166</t>
         </is>
@@ -12023,7 +12053,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -12081,7 +12111,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -12139,7 +12169,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -12197,7 +12227,7 @@
           <t>CHOOAMPAI Rattanajet</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>51801</t>
         </is>
@@ -12255,7 +12285,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -12313,7 +12343,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -12371,7 +12401,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -12482,7 +12512,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -12540,7 +12570,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -12598,7 +12628,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -12656,7 +12686,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -12714,7 +12744,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -12772,7 +12802,7 @@
           <t>COF Blaz</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>36897</t>
         </is>
@@ -12830,7 +12860,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -12888,7 +12918,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -12946,7 +12976,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -13004,7 +13034,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -13062,7 +13092,7 @@
           <t>ZHANG Jinjie</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>72213</t>
         </is>
@@ -13120,7 +13150,7 @@
           <t>WALL Demelza</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>60107</t>
         </is>
@@ -13178,7 +13208,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -13236,7 +13266,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -13400,7 +13430,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -13458,7 +13488,7 @@
           <t>KUBBE Kira</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
@@ -13516,7 +13546,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -13574,7 +13604,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -13791,7 +13821,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -13849,7 +13879,7 @@
           <t>NAVEAU Laurine</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>53246</t>
         </is>
@@ -13907,7 +13937,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -14018,7 +14048,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -14076,7 +14106,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -14134,7 +14164,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -14192,7 +14222,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -14250,7 +14280,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -14308,7 +14338,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -14366,7 +14396,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -14424,7 +14454,7 @@
           <t>LAUNAY Damien</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>60047</t>
         </is>
@@ -14482,7 +14512,7 @@
           <t>SHABAKIN Mikhail</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>73958</t>
         </is>
@@ -14540,7 +14570,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -14598,7 +14628,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -14656,7 +14686,7 @@
           <t>MUSGRAVE Andrew</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>60102</t>
         </is>
@@ -14714,7 +14744,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -14772,7 +14802,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -14830,7 +14860,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -14888,7 +14918,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -14946,7 +14976,7 @@
           <t>PROZHERIN Artem</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>35775</t>
         </is>
@@ -15004,7 +15034,7 @@
           <t>TRAVOSTINO Benjamin</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>68795</t>
         </is>
@@ -15062,7 +15092,7 @@
           <t>SANDERA Wiktor</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>53642</t>
         </is>
@@ -15120,7 +15150,7 @@
           <t>LEE EDWARDS Ciaran</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>35614</t>
         </is>
@@ -15178,7 +15208,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -15236,7 +15266,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -15294,7 +15324,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -15405,7 +15435,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -15463,7 +15493,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -15521,7 +15551,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -15579,7 +15609,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -15637,7 +15667,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -15695,7 +15725,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -15753,7 +15783,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -15811,7 +15841,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -15869,7 +15899,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -15927,7 +15957,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -15985,7 +16015,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -16043,7 +16073,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -16101,7 +16131,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -16159,7 +16189,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -16217,7 +16247,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -16275,7 +16305,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -16333,7 +16363,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -16391,7 +16421,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -16449,7 +16479,7 @@
           <t>DAILLE Etienne</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>35308</t>
         </is>
@@ -16507,7 +16537,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -16565,7 +16595,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -16676,7 +16706,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -16734,7 +16764,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -16792,7 +16822,7 @@
           <t>ILIUKHINA Polina</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>68830</t>
         </is>
@@ -16850,7 +16880,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -16908,7 +16938,7 @@
           <t>KAIFUCHI Moe</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>36483</t>
         </is>
@@ -16966,7 +16996,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -17024,7 +17054,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -17082,7 +17112,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -17140,7 +17170,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -17198,7 +17228,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -17256,7 +17286,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -17314,7 +17344,7 @@
           <t>FAGERLUND Amanda</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>43406</t>
         </is>
@@ -17425,7 +17455,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -17536,7 +17566,7 @@
           <t>HASSOVA Michaela</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>41783</t>
         </is>
@@ -17594,7 +17624,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -17652,7 +17682,7 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -17710,7 +17740,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -17768,7 +17798,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -17826,7 +17856,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -17884,7 +17914,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -17942,7 +17972,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -18053,7 +18083,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -18164,7 +18194,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -18222,7 +18252,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -18280,7 +18310,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -18338,7 +18368,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -18396,7 +18426,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -18454,7 +18484,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -18512,7 +18542,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -18570,7 +18600,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -18628,7 +18658,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -18686,7 +18716,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -18744,7 +18774,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -18802,7 +18832,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -18860,7 +18890,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -18918,7 +18948,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -18976,7 +19006,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -19087,7 +19117,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -19198,7 +19228,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -19256,7 +19286,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -19314,7 +19344,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -19372,7 +19402,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -19430,7 +19460,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -19488,7 +19518,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -19546,6 +19576,11 @@
           <t>FOX Jessica</t>
         </is>
       </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>36526</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -19604,12 +19639,12 @@
           <t>XIE Yuancong</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>42912</t>
         </is>
       </c>
-      <c r="V335" t="inlineStr">
+      <c r="Y335" t="inlineStr">
         <is>
           <t>72214</t>
         </is>
@@ -19672,12 +19707,12 @@
           <t>WEBER Alexander</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>51833</t>
         </is>
       </c>
-      <c r="V336" t="inlineStr">
+      <c r="Y336" t="inlineStr">
         <is>
           <t>51832</t>
         </is>
@@ -19740,12 +19775,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V337" t="inlineStr">
+      <c r="Y337" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -19808,12 +19843,12 @@
           <t>DENG Xiao</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="V338" t="inlineStr">
+      <c r="Y338" t="inlineStr">
         <is>
           <t>42240</t>
         </is>
@@ -19876,12 +19911,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V339" t="inlineStr">
+      <c r="Y339" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -19944,12 +19979,12 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
       </c>
-      <c r="V340" t="inlineStr">
+      <c r="Y340" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -20012,12 +20047,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V341" t="inlineStr">
+      <c r="Y341" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -20080,12 +20115,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V342" t="inlineStr">
+      <c r="Y342" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -20148,12 +20183,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V343" t="inlineStr">
+      <c r="Y343" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -20216,12 +20251,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V344" t="inlineStr">
+      <c r="Y344" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -20284,12 +20319,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V345" t="inlineStr">
+      <c r="Y345" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -20352,12 +20387,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V346" t="inlineStr">
+      <c r="Y346" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -20420,12 +20455,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V347" t="inlineStr">
+      <c r="Y347" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -20488,12 +20523,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V348" t="inlineStr">
+      <c r="Y348" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -20556,12 +20591,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V349" t="inlineStr">
+      <c r="Y349" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -20624,12 +20659,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V350" t="inlineStr">
+      <c r="Y350" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -20692,12 +20727,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V351" t="inlineStr">
+      <c r="Y351" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -20760,12 +20795,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V352" t="inlineStr">
+      <c r="Y352" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -20828,12 +20863,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V353" t="inlineStr">
+      <c r="Y353" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -20896,12 +20931,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V354" t="inlineStr">
+      <c r="Y354" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -20964,12 +20999,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V355" t="inlineStr">
+      <c r="Y355" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -21032,12 +21067,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V356" t="inlineStr">
+      <c r="Y356" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -21100,12 +21135,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V357" t="inlineStr">
+      <c r="Y357" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -21168,12 +21203,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V358" t="inlineStr">
+      <c r="Y358" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -21236,12 +21271,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V359" t="inlineStr">
+      <c r="Y359" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -21352,7 +21387,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -21410,7 +21445,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -21468,7 +21503,7 @@
           <t>ILIUKHINA Polina</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>68830</t>
         </is>
@@ -21526,7 +21561,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -21584,7 +21619,7 @@
           <t>KAIFUCHI Moe</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>36483</t>
         </is>
@@ -21642,7 +21677,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -21700,7 +21735,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -21758,7 +21793,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -21816,7 +21851,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -21874,7 +21909,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -21932,7 +21967,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -21990,7 +22025,7 @@
           <t>FAGERLUND Amanda</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>43406</t>
         </is>
@@ -22101,7 +22136,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -22212,7 +22247,7 @@
           <t>HASSOVA Michaela</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>41783</t>
         </is>
@@ -22270,7 +22305,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -22328,7 +22363,7 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -22386,7 +22421,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -22444,7 +22479,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -22502,7 +22537,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -22560,7 +22595,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -22618,7 +22653,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -22676,7 +22711,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -22734,7 +22769,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -22792,7 +22827,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -22850,7 +22885,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -22908,7 +22943,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -22966,7 +23001,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -23077,7 +23112,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -23135,7 +23170,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -23198,12 +23233,12 @@
           <t>WEBER Alexander</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>51833</t>
         </is>
       </c>
-      <c r="V393" t="inlineStr">
+      <c r="Y393" t="inlineStr">
         <is>
           <t>51832</t>
         </is>
@@ -23266,12 +23301,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V394" t="inlineStr">
+      <c r="Y394" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -23334,12 +23369,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V395" t="inlineStr">
+      <c r="Y395" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -23402,12 +23437,12 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
       </c>
-      <c r="V396" t="inlineStr">
+      <c r="Y396" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -23470,12 +23505,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V397" t="inlineStr">
+      <c r="Y397" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -23538,12 +23573,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V398" t="inlineStr">
+      <c r="Y398" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -23606,12 +23641,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V399" t="inlineStr">
+      <c r="Y399" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -23674,12 +23709,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V400" t="inlineStr">
+      <c r="Y400" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -23742,12 +23777,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V401" t="inlineStr">
+      <c r="Y401" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -23810,12 +23845,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V402" t="inlineStr">
+      <c r="Y402" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -24191,7 +24226,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -24249,7 +24284,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -24307,7 +24342,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -24365,7 +24400,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -24476,7 +24511,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -24534,7 +24569,7 @@
           <t>COF Blaz</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>36897</t>
         </is>
@@ -24592,7 +24627,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -24650,7 +24685,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -24708,7 +24743,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -24766,7 +24801,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -24824,7 +24859,7 @@
           <t>FOULON Kilian</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>35602</t>
         </is>
@@ -24882,7 +24917,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -24940,7 +24975,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -24998,7 +25033,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -25056,7 +25091,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -25114,7 +25149,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -25172,7 +25207,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -25230,7 +25265,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -25288,7 +25323,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -25346,7 +25381,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -25404,7 +25439,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -25462,7 +25497,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -25520,7 +25555,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -25578,7 +25613,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -25636,7 +25671,7 @@
           <t>BREUER Florian</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>39171</t>
         </is>
@@ -25694,7 +25729,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -25752,7 +25787,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -25810,7 +25845,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -25868,7 +25903,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -25926,7 +25961,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -25984,7 +26019,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -26095,7 +26130,7 @@
           <t>KUBBE Kira</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
@@ -26153,7 +26188,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -26211,7 +26246,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -26269,7 +26304,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -26433,7 +26468,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -26491,7 +26526,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -26549,7 +26584,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -26607,7 +26642,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -26665,7 +26700,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -26723,7 +26758,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -26781,7 +26816,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -26892,7 +26927,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -26950,7 +26985,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -27008,7 +27043,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -27066,7 +27101,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -27124,7 +27159,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -27182,7 +27217,7 @@
           <t>DAILLE Etienne</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35308</t>
         </is>
@@ -27240,7 +27275,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -27298,7 +27333,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -27356,7 +27391,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -27414,7 +27449,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -27472,7 +27507,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -27530,7 +27565,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -27588,7 +27623,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -27646,7 +27681,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -27704,7 +27739,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -27762,7 +27797,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -27820,7 +27855,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -27878,7 +27913,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -27936,7 +27971,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -27994,7 +28029,7 @@
           <t>CADENA Jordi</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>41644</t>
         </is>
@@ -28052,7 +28087,7 @@
           <t>HUJSA Matus</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>35503</t>
         </is>
@@ -28110,7 +28145,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -28168,7 +28203,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -28226,7 +28261,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -28284,7 +28319,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -28342,7 +28377,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -28400,7 +28435,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -28458,7 +28493,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -28516,7 +28551,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -28574,7 +28609,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -28632,7 +28667,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -28690,7 +28725,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -28748,7 +28783,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -28806,7 +28841,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -28864,7 +28899,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -28922,7 +28957,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -29033,7 +29068,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -29091,7 +29126,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -29149,7 +29184,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -29207,7 +29242,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -29265,7 +29300,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -29323,7 +29358,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -29391,7 +29426,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -29459,7 +29494,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -29527,7 +29562,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -29595,7 +29630,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -29663,7 +29698,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -29731,7 +29766,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -29799,7 +29834,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -29867,7 +29902,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -29935,7 +29970,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -30003,7 +30038,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -30071,7 +30106,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -30202,7 +30237,7 @@
           <t>KUBBE Kira</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>43464</t>
         </is>
@@ -30270,7 +30305,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -30338,7 +30373,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -30469,7 +30504,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -30537,7 +30572,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -30605,7 +30640,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -30673,7 +30708,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -30741,7 +30776,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -30809,7 +30844,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -30877,7 +30912,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -30945,7 +30980,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -31013,7 +31048,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -31081,7 +31116,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -31149,7 +31184,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -31217,7 +31252,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -31285,7 +31320,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -31353,7 +31388,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -31623,7 +31658,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -31681,7 +31716,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -31739,7 +31774,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -31797,7 +31832,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -31908,7 +31943,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -31966,7 +32001,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -32024,7 +32059,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -32082,7 +32117,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -32140,7 +32175,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -32198,7 +32233,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -32256,7 +32291,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -32314,7 +32349,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -32372,7 +32407,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -32483,7 +32518,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -32541,7 +32576,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -32599,7 +32634,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -32657,7 +32692,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -32715,7 +32750,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -32826,7 +32861,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -32884,7 +32919,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -32942,7 +32977,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -33000,7 +33035,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -33058,7 +33093,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -33169,7 +33204,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -33227,6 +33262,11 @@
           <t>FOX Jessica</t>
         </is>
       </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>36526</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -33280,7 +33320,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -33343,12 +33383,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V563" t="inlineStr">
+      <c r="Y563" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -33411,12 +33451,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V564" t="inlineStr">
+      <c r="Y564" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -33479,12 +33519,12 @@
           <t>WEBER Alexander</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>51833</t>
         </is>
       </c>
-      <c r="V565" t="inlineStr">
+      <c r="Y565" t="inlineStr">
         <is>
           <t>51832</t>
         </is>
@@ -33547,12 +33587,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V566" t="inlineStr">
+      <c r="Y566" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -33615,12 +33655,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V567" t="inlineStr">
+      <c r="Y567" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -33683,12 +33723,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V568" t="inlineStr">
+      <c r="Y568" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -33751,12 +33791,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V569" t="inlineStr">
+      <c r="Y569" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -33819,12 +33859,12 @@
           <t>DENG Xiao</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="V570" t="inlineStr">
+      <c r="Y570" t="inlineStr">
         <is>
           <t>42240</t>
         </is>
@@ -33887,12 +33927,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V571" t="inlineStr">
+      <c r="Y571" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -33955,12 +33995,12 @@
           <t>XIE Yuancong</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>42912</t>
         </is>
       </c>
-      <c r="V572" t="inlineStr">
+      <c r="Y572" t="inlineStr">
         <is>
           <t>72214</t>
         </is>
@@ -34023,12 +34063,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V573" t="inlineStr">
+      <c r="Y573" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -34091,12 +34131,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V574" t="inlineStr">
+      <c r="Y574" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -34159,12 +34199,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V575" t="inlineStr">
+      <c r="Y575" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -34227,12 +34267,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V576" t="inlineStr">
+      <c r="Y576" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -34295,12 +34335,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V577" t="inlineStr">
+      <c r="Y577" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -34363,12 +34403,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V578" t="inlineStr">
+      <c r="Y578" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -34431,12 +34471,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V579" t="inlineStr">
+      <c r="Y579" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -34499,12 +34539,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V580" t="inlineStr">
+      <c r="Y580" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -34567,12 +34607,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V581" t="inlineStr">
+      <c r="Y581" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -34635,12 +34675,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V582" t="inlineStr">
+      <c r="Y582" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -34708,7 +34748,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -34776,7 +34816,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -34844,7 +34884,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -34912,7 +34952,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -34980,7 +35020,7 @@
           <t>MANGIN Estelle</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>35670</t>
         </is>
@@ -35111,7 +35151,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -35179,7 +35219,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -35247,7 +35287,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -35315,7 +35355,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -35388,12 +35428,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V593" t="inlineStr">
+      <c r="Y593" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -35466,12 +35506,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V594" t="inlineStr">
+      <c r="Y594" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -35544,12 +35584,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V595" t="inlineStr">
+      <c r="Y595" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -35622,12 +35662,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V596" t="inlineStr">
+      <c r="Y596" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -35700,12 +35740,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V597" t="inlineStr">
+      <c r="Y597" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -35778,12 +35818,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V598" t="inlineStr">
+      <c r="Y598" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -35856,12 +35896,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V599" t="inlineStr">
+      <c r="Y599" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -35934,12 +35974,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V600" t="inlineStr">
+      <c r="Y600" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -36012,12 +36052,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V601" t="inlineStr">
+      <c r="Y601" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -36090,12 +36130,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V602" t="inlineStr">
+      <c r="Y602" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
